--- a/consent_forms/047_corporate_banking_relationship_consent_form--consent_forms.xlsx
+++ b/consent_forms/047_corporate_banking_relationship_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'individual',_'label':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Individual', 'label': 'Individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'business',_'label':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Business', 'label': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'government_institution',_'label':_'government_institution'}</t>
+          <t>government_institution</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Government Institution', 'label': 'Government Institution'}</t>
+          <t>Government Institution</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'given',_'label':_'given'}</t>
+          <t>given</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Given', 'label': 'Given'}</t>
+          <t>Given</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_given',_'label':_'not_given'}</t>
+          <t>not_given</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Not Given', 'label': 'Not Given'}</t>
+          <t>Not Given</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'signature_1',_'label':_'signature_1'}</t>
+          <t>signature_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Signature 1', 'label': 'Signature 1'}</t>
+          <t>Signature 1</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'signature_2',_'label':_'signature_2'}</t>
+          <t>signature_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Signature 2', 'label': 'Signature 2'}</t>
+          <t>Signature 2</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'signature_3',_'label':_'signature_3'}</t>
+          <t>signature_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Signature 3', 'label': 'Signature 3'}</t>
+          <t>Signature 3</t>
         </is>
       </c>
     </row>
